--- a/tame_output/MOZAIC/data/universe_last2023-07-21.xlsx
+++ b/tame_output/MOZAIC/data/universe_last2023-07-21.xlsx
@@ -513,19 +513,19 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>580.4601584390475</v>
+        <v>581.3719119904275</v>
       </c>
       <c r="E2" t="n">
-        <v>11208.72748503706</v>
+        <v>11136.61385880884</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6876343537589729</v>
+        <v>0.6900533488159319</v>
       </c>
       <c r="G2" t="n">
-        <v>0.5037011992918615</v>
+        <v>0.5037048161548103</v>
       </c>
       <c r="H2" t="n">
-        <v>1.365163225193225</v>
+        <v>1.369955828661064</v>
       </c>
       <c r="I2" t="n">
         <v>0.2590724514387045</v>
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>227.6842332262667</v>
+        <v>227.9043235105253</v>
       </c>
       <c r="E3" t="n">
-        <v>4821.437886312836</v>
+        <v>4745.134248035822</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2945322739095142</v>
+        <v>0.2949496200519544</v>
       </c>
       <c r="G3" t="n">
-        <v>0.6047186821420792</v>
+        <v>0.6047188287888201</v>
       </c>
       <c r="H3" t="n">
-        <v>0.4870566804157599</v>
+        <v>0.4877467113810618</v>
       </c>
       <c r="I3" t="n">
         <v>0.3295577524045769</v>
@@ -598,10 +598,10 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>0.8909096616898828</v>
+        <v>0.8909056880520033</v>
       </c>
       <c r="N3" t="n">
-        <v>1.069581961055808</v>
+        <v>1.069569769756827</v>
       </c>
     </row>
     <row r="4">
@@ -621,19 +621,19 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>41.1109346713336</v>
+        <v>41.05169092271853</v>
       </c>
       <c r="E4" t="n">
-        <v>1978.391292213524</v>
+        <v>1910.389761217617</v>
       </c>
       <c r="F4" t="n">
-        <v>1.065820074096855</v>
+        <v>1.042052158414431</v>
       </c>
       <c r="G4" t="n">
-        <v>1.119324247053596</v>
+        <v>1.119543472121109</v>
       </c>
       <c r="H4" t="n">
-        <v>0.9521995765770467</v>
+        <v>0.9307831132632465</v>
       </c>
       <c r="I4" t="n">
         <v>0.3422195892575038</v>
@@ -652,10 +652,10 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>0.4718818335908732</v>
+        <v>0.471705456719753</v>
       </c>
       <c r="N4" t="n">
-        <v>1.048615287843148</v>
+        <v>1.048421114703417</v>
       </c>
     </row>
     <row r="5">
@@ -675,19 +675,19 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>37.49723937467857</v>
+        <v>37.53606526569085</v>
       </c>
       <c r="E5" t="n">
-        <v>418.3165772060192</v>
+        <v>417.0844827695108</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.3309897492190856</v>
+        <v>-0.3317512968627633</v>
       </c>
       <c r="G5" t="n">
-        <v>0.5683197560479892</v>
+        <v>0.5683110813757948</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.5824005688641531</v>
+        <v>-0.5837494775918214</v>
       </c>
       <c r="I5" t="n">
         <v>0.3496897913141569</v>
@@ -706,10 +706,10 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>0.7367378241212524</v>
+        <v>0.736760359506909</v>
       </c>
       <c r="N5" t="n">
-        <v>0.8312520618663565</v>
+        <v>0.8312588309608364</v>
       </c>
     </row>
     <row r="6">
@@ -729,19 +729,19 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>10.97509812665906</v>
+        <v>10.9627800219663</v>
       </c>
       <c r="E6" t="n">
-        <v>219.0674936068508</v>
+        <v>213.71085559381</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.3003109176812296</v>
+        <v>-0.304952781492719</v>
       </c>
       <c r="G6" t="n">
-        <v>0.7217689126055262</v>
+        <v>0.7218621353633526</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.4160762710008277</v>
+        <v>-0.4224529401853439</v>
       </c>
       <c r="I6" t="n">
         <v>0.4277673545966229</v>
@@ -760,10 +760,10 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>0.7501394278640541</v>
+        <v>0.7499738277324458</v>
       </c>
       <c r="N6" t="n">
-        <v>1.074897816231421</v>
+        <v>1.074791606890615</v>
       </c>
     </row>
     <row r="7">
@@ -783,19 +783,19 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>10.41731251648016</v>
+        <v>10.38726023410021</v>
       </c>
       <c r="E7" t="n">
-        <v>421.8056493897286</v>
+        <v>411.9822305997635</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.2775564287467178</v>
+        <v>-0.2818343007758044</v>
       </c>
       <c r="G7" t="n">
-        <v>1.180492263653923</v>
+        <v>1.180433237185234</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.235119227200702</v>
+        <v>-0.2387549688518122</v>
       </c>
       <c r="I7" t="n">
         <v>0.7387533875338753</v>
@@ -814,10 +814,10 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>0.7386402590525827</v>
+        <v>0.7386870532775983</v>
       </c>
       <c r="N7" t="n">
-        <v>1.731103901798854</v>
+        <v>1.731114576635897</v>
       </c>
     </row>
     <row r="8">
@@ -837,19 +837,19 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>10.27273617526942</v>
+        <v>10.3018645970276</v>
       </c>
       <c r="E8" t="n">
-        <v>742.0537858385603</v>
+        <v>746.4231518722319</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.5331872121113352</v>
+        <v>-0.5305324884502591</v>
       </c>
       <c r="G8" t="n">
-        <v>0.8116337757037136</v>
+        <v>0.8119272427410865</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.6569307834054147</v>
+        <v>-0.6534236819781638</v>
       </c>
       <c r="I8" t="n">
         <v>0.5751178664414889</v>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>0.6837594733675685</v>
+        <v>0.6836676584138365</v>
       </c>
       <c r="N8" t="n">
-        <v>1.101768834028403</v>
+        <v>1.102011295195952</v>
       </c>
     </row>
     <row r="9">
@@ -891,19 +891,19 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>7.260314694096711</v>
+        <v>7.257150331777682</v>
       </c>
       <c r="E9" t="n">
-        <v>166.3827752291137</v>
+        <v>164.9194414775531</v>
       </c>
       <c r="F9" t="n">
-        <v>0.4076401233383946</v>
+        <v>0.4040201285942755</v>
       </c>
       <c r="G9" t="n">
-        <v>0.4826814079651873</v>
+        <v>0.4826805244371472</v>
       </c>
       <c r="H9" t="n">
-        <v>0.8445324734111057</v>
+        <v>0.8370342455092892</v>
       </c>
       <c r="I9" t="n">
         <v>0.2154834665412946</v>
@@ -922,10 +922,10 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>0.6830716996097165</v>
+        <v>0.6830555734829968</v>
       </c>
       <c r="N9" t="n">
-        <v>0.654566656129299</v>
+        <v>0.6545453048182865</v>
       </c>
     </row>
     <row r="10">
@@ -945,19 +945,19 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>7.207502417403274</v>
+        <v>7.196336088817682</v>
       </c>
       <c r="E10" t="n">
-        <v>264.2028048479028</v>
+        <v>261.3952331292615</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.1935510466187688</v>
+        <v>-0.1980360012199773</v>
       </c>
       <c r="G10" t="n">
-        <v>0.9683405482064232</v>
+        <v>0.9683185709702108</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.1998791096554485</v>
+        <v>-0.2045153394316855</v>
       </c>
       <c r="I10" t="n">
         <v>0.6126386245816655</v>
@@ -976,10 +976,10 @@
         </is>
       </c>
       <c r="M10" t="n">
-        <v>0.7132357983604757</v>
+        <v>0.7132434911383944</v>
       </c>
       <c r="N10" t="n">
-        <v>1.371160412077239</v>
+        <v>1.37113423565255</v>
       </c>
     </row>
     <row r="11">
@@ -999,19 +999,19 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>6.916686866143337</v>
+        <v>6.947648675735286</v>
       </c>
       <c r="E11" t="n">
-        <v>221.5923034747266</v>
+        <v>223.5976023234206</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.2295404944027419</v>
+        <v>-0.2281757963002916</v>
       </c>
       <c r="G11" t="n">
-        <v>0.6645597182669347</v>
+        <v>0.6646278686940342</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.3454023590255316</v>
+        <v>-0.3433136151041145</v>
       </c>
       <c r="I11" t="n">
         <v>0.4207389749702026</v>
@@ -1030,10 +1030,10 @@
         </is>
       </c>
       <c r="M11" t="n">
-        <v>0.7886730838142899</v>
+        <v>0.7887005675498857</v>
       </c>
       <c r="N11" t="n">
-        <v>1.040538245930692</v>
+        <v>1.04067374469445</v>
       </c>
     </row>
     <row r="12">
@@ -1053,19 +1053,19 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>6.886975543340435</v>
+        <v>6.897476547321964</v>
       </c>
       <c r="E12" t="n">
-        <v>474.1800271225367</v>
+        <v>464.3456260135105</v>
       </c>
       <c r="F12" t="n">
-        <v>1.09567722394335</v>
+        <v>1.097849180532594</v>
       </c>
       <c r="G12" t="n">
-        <v>0.8297965700672022</v>
+        <v>0.8298120817556376</v>
       </c>
       <c r="H12" t="n">
-        <v>1.320416670141955</v>
+        <v>1.323009395343906</v>
       </c>
       <c r="I12" t="n">
         <v>0.3268819295856837</v>
@@ -1084,10 +1084,10 @@
         </is>
       </c>
       <c r="M12" t="n">
-        <v>0.6626942999701616</v>
+        <v>0.6627224123525529</v>
       </c>
       <c r="N12" t="n">
-        <v>1.091721556135693</v>
+        <v>1.091780437635067</v>
       </c>
     </row>
     <row r="13">
@@ -1107,19 +1107,19 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>4.821221846093657</v>
+        <v>4.82925591340638</v>
       </c>
       <c r="E13" t="n">
-        <v>102.2710032170419</v>
+        <v>101.0197736586972</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.3617894863635805</v>
+        <v>-0.363058996185505</v>
       </c>
       <c r="G13" t="n">
-        <v>0.859613001227609</v>
+        <v>0.8596025375910525</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.4208748423382508</v>
+        <v>-0.4223568222622287</v>
       </c>
       <c r="I13" t="n">
         <v>0.4691011235955056</v>
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="M13" t="n">
-        <v>0.7603723955462879</v>
+        <v>0.760385259670406</v>
       </c>
       <c r="N13" t="n">
-        <v>1.29764629884758</v>
+        <v>1.297643138990007</v>
       </c>
     </row>
     <row r="14">
@@ -1161,19 +1161,19 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>4.799224923934766</v>
+        <v>4.813855107047473</v>
       </c>
       <c r="E14" t="n">
-        <v>197.8488651331012</v>
+        <v>194.0849738246058</v>
       </c>
       <c r="F14" t="n">
-        <v>1.887454545481823</v>
+        <v>1.895572967645</v>
       </c>
       <c r="G14" t="n">
-        <v>0.8681290929862739</v>
+        <v>0.8681583852948888</v>
       </c>
       <c r="H14" t="n">
-        <v>2.174163451876927</v>
+        <v>2.183441408564093</v>
       </c>
       <c r="I14" t="n">
         <v>0.3000688231245698</v>
@@ -1192,10 +1192,10 @@
         </is>
       </c>
       <c r="M14" t="n">
-        <v>0.6021388626226777</v>
+        <v>0.6021518474963754</v>
       </c>
       <c r="N14" t="n">
-        <v>1.037786420590835</v>
+        <v>1.037836365384522</v>
       </c>
     </row>
     <row r="15">
@@ -1215,19 +1215,19 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>4.378664135424605</v>
+        <v>4.37142206673539</v>
       </c>
       <c r="E15" t="n">
-        <v>708.1435420156773</v>
+        <v>681.6620630120982</v>
       </c>
       <c r="F15" t="n">
-        <v>0.05105111613226709</v>
+        <v>0.04371472593327974</v>
       </c>
       <c r="G15" t="n">
-        <v>0.7986019402257832</v>
+        <v>0.7988500589039178</v>
       </c>
       <c r="H15" t="n">
-        <v>0.063925609945092</v>
+        <v>0.0547220663578089</v>
       </c>
       <c r="I15" t="n">
         <v>0.4268646717284502</v>
@@ -1246,10 +1246,10 @@
         </is>
       </c>
       <c r="M15" t="n">
-        <v>0.7171075926554806</v>
+        <v>0.7167542938177917</v>
       </c>
       <c r="N15" t="n">
-        <v>1.136950866208828</v>
+        <v>1.136735626645271</v>
       </c>
     </row>
     <row r="16">
@@ -1269,19 +1269,19 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>4.339310886865078</v>
+        <v>4.320072916529446</v>
       </c>
       <c r="E16" t="n">
-        <v>381.9036776215827</v>
+        <v>370.0369556812129</v>
       </c>
       <c r="F16" t="n">
-        <v>0.6405066881913821</v>
+        <v>0.6290625364289599</v>
       </c>
       <c r="G16" t="n">
-        <v>0.9654528109065363</v>
+        <v>0.9656664002290563</v>
       </c>
       <c r="H16" t="n">
-        <v>0.6634261985212536</v>
+        <v>0.6514284190479717</v>
       </c>
       <c r="I16" t="n">
         <v>0.3858131487889274</v>
@@ -1300,10 +1300,10 @@
         </is>
       </c>
       <c r="M16" t="n">
-        <v>0.5133283253447338</v>
+        <v>0.5131038238708179</v>
       </c>
       <c r="N16" t="n">
-        <v>0.9839052901179497</v>
+        <v>0.9836854972393428</v>
       </c>
     </row>
     <row r="17">
@@ -1323,19 +1323,19 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>3.590126816550678</v>
+        <v>3.597518089330997</v>
       </c>
       <c r="E17" t="n">
-        <v>144.695908179744</v>
+        <v>145.0249844792187</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.144636552715534</v>
+        <v>-0.1442547629139544</v>
       </c>
       <c r="G17" t="n">
-        <v>0.7584878589541731</v>
+        <v>0.7585081619513988</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.1906906630186057</v>
+        <v>-0.1901822157626269</v>
       </c>
       <c r="I17" t="n">
         <v>0.4720416124837452</v>
@@ -1354,10 +1354,10 @@
         </is>
       </c>
       <c r="M17" t="n">
-        <v>0.7228483762912035</v>
+        <v>0.7229508629889076</v>
       </c>
       <c r="N17" t="n">
-        <v>1.088486027137546</v>
+        <v>1.088661677791776</v>
       </c>
     </row>
     <row r="18">
@@ -1377,19 +1377,19 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>3.268100467191358</v>
+        <v>3.275535649535071</v>
       </c>
       <c r="E18" t="n">
-        <v>70.55120067120573</v>
+        <v>70.08529916224686</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.4398431152380354</v>
+        <v>-0.4399255442547443</v>
       </c>
       <c r="G18" t="n">
-        <v>0.7545793421584865</v>
+        <v>0.7545779741262876</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.582898431833367</v>
+        <v>-0.5830087271817419</v>
       </c>
       <c r="I18" t="n">
         <v>0.4644343302990898</v>
@@ -1408,10 +1408,10 @@
         </is>
       </c>
       <c r="M18" t="n">
-        <v>0.7641705459339769</v>
+        <v>0.7641923008506487</v>
       </c>
       <c r="N18" t="n">
-        <v>1.144780494186662</v>
+        <v>1.144802788706236</v>
       </c>
     </row>
     <row r="19">
@@ -1431,19 +1431,19 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>3.002675823463201</v>
+        <v>2.998233406709849</v>
       </c>
       <c r="E19" t="n">
-        <v>110.8485060242421</v>
+        <v>109.8086863677731</v>
       </c>
       <c r="F19" t="n">
-        <v>0.1331514814441546</v>
+        <v>0.135073286169676</v>
       </c>
       <c r="G19" t="n">
-        <v>0.4863115920767929</v>
+        <v>0.4862681719613752</v>
       </c>
       <c r="H19" t="n">
-        <v>0.2737986994624811</v>
+        <v>0.2777752975788121</v>
       </c>
       <c r="I19" t="n">
         <v>0.2812667740203972</v>
@@ -1462,10 +1462,10 @@
         </is>
       </c>
       <c r="M19" t="n">
-        <v>0.7185031003410621</v>
+        <v>0.7184967821852415</v>
       </c>
       <c r="N19" t="n">
-        <v>0.6936977460649445</v>
+        <v>0.6936247294605331</v>
       </c>
     </row>
     <row r="20">
@@ -1485,19 +1485,19 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>2.658725521568095</v>
+        <v>2.65922158515475</v>
       </c>
       <c r="E20" t="n">
-        <v>116.2760939689572</v>
+        <v>114.6212853911332</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.3028036033017144</v>
+        <v>-0.3038382463367422</v>
       </c>
       <c r="G20" t="n">
-        <v>0.7873035163765394</v>
+        <v>0.7873042411171082</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.3846084731023787</v>
+        <v>-0.3859222781597432</v>
       </c>
       <c r="I20" t="n">
         <v>0.443815987933635</v>
@@ -1516,10 +1516,10 @@
         </is>
       </c>
       <c r="M20" t="n">
-        <v>0.7320265651758621</v>
+        <v>0.732014496190137</v>
       </c>
       <c r="N20" t="n">
-        <v>1.144184468201062</v>
+        <v>1.144158441464198</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/MOZAIC/data/universe_last2023-07-21.xlsx
+++ b/tame_output/MOZAIC/data/universe_last2023-07-21.xlsx
@@ -513,19 +513,19 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>581.3719119904275</v>
+        <v>581.8129676216543</v>
       </c>
       <c r="E2" t="n">
-        <v>11136.61385880884</v>
+        <v>10974.52677257587</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6900533488159319</v>
+        <v>0.6916213117292849</v>
       </c>
       <c r="G2" t="n">
-        <v>0.5037048161548103</v>
+        <v>0.5037087147506278</v>
       </c>
       <c r="H2" t="n">
-        <v>1.369955828661064</v>
+        <v>1.373058062081946</v>
       </c>
       <c r="I2" t="n">
         <v>0.2590724514387045</v>
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>227.9043235105253</v>
+        <v>227.9470433499902</v>
       </c>
       <c r="E3" t="n">
-        <v>4745.134248035822</v>
+        <v>4684.236035670167</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2949496200519544</v>
+        <v>0.2946271220043644</v>
       </c>
       <c r="G3" t="n">
-        <v>0.6047188287888201</v>
+        <v>0.6047187047164361</v>
       </c>
       <c r="H3" t="n">
-        <v>0.4877467113810618</v>
+        <v>0.4872135088702449</v>
       </c>
       <c r="I3" t="n">
         <v>0.3295577524045769</v>
@@ -598,10 +598,10 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>0.8909056880520033</v>
+        <v>0.8908981672270467</v>
       </c>
       <c r="N3" t="n">
-        <v>1.069569769756827</v>
+        <v>1.069552243078627</v>
       </c>
     </row>
     <row r="4">
@@ -621,19 +621,19 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>41.05169092271853</v>
+        <v>40.70623346966742</v>
       </c>
       <c r="E4" t="n">
-        <v>1910.389761217617</v>
+        <v>1873.558364564341</v>
       </c>
       <c r="F4" t="n">
-        <v>1.042052158414431</v>
+        <v>1.033660409935516</v>
       </c>
       <c r="G4" t="n">
-        <v>1.119543472121109</v>
+        <v>1.119640648982156</v>
       </c>
       <c r="H4" t="n">
-        <v>0.9307831132632465</v>
+        <v>0.9232072905491568</v>
       </c>
       <c r="I4" t="n">
         <v>0.3422195892575038</v>
@@ -652,10 +652,10 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>0.471705456719753</v>
+        <v>0.4716011478790175</v>
       </c>
       <c r="N4" t="n">
-        <v>1.048421114703417</v>
+        <v>1.048272145804352</v>
       </c>
     </row>
     <row r="5">
@@ -675,19 +675,19 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>37.53606526569085</v>
+        <v>37.52182154641338</v>
       </c>
       <c r="E5" t="n">
-        <v>417.0844827695108</v>
+        <v>414.2290470393924</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.3317512968627633</v>
+        <v>-0.3309897492190856</v>
       </c>
       <c r="G5" t="n">
-        <v>0.5683110813757948</v>
+        <v>0.5683197560479892</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.5837494775918214</v>
+        <v>-0.5824005688641531</v>
       </c>
       <c r="I5" t="n">
         <v>0.3496897913141569</v>
@@ -706,10 +706,10 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>0.736760359506909</v>
+        <v>0.7367658595825548</v>
       </c>
       <c r="N5" t="n">
-        <v>0.8312588309608364</v>
+        <v>0.831271290967718</v>
       </c>
     </row>
     <row r="6">
@@ -729,19 +729,19 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>10.9627800219663</v>
+        <v>10.95388873837297</v>
       </c>
       <c r="E6" t="n">
-        <v>213.71085559381</v>
+        <v>207.6948224905358</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.304952781492719</v>
+        <v>-0.3018591648373</v>
       </c>
       <c r="G6" t="n">
-        <v>0.7218621353633526</v>
+        <v>0.7217952433476782</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.4224529401853439</v>
+        <v>-0.4182060876950098</v>
       </c>
       <c r="I6" t="n">
         <v>0.4277673545966229</v>
@@ -760,10 +760,10 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>0.7499738277324458</v>
+        <v>0.7500348382924856</v>
       </c>
       <c r="N6" t="n">
-        <v>1.074791606890615</v>
+        <v>1.074771118249521</v>
       </c>
     </row>
     <row r="7">
@@ -783,19 +783,19 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>10.38726023410021</v>
+        <v>10.42603281206487</v>
       </c>
       <c r="E7" t="n">
-        <v>411.9822305997635</v>
+        <v>408.0746393534303</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.2818343007758044</v>
+        <v>-0.2756095963649136</v>
       </c>
       <c r="G7" t="n">
-        <v>1.180433237185234</v>
+        <v>1.180526293167712</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.2387549688518122</v>
+        <v>-0.2334633272973268</v>
       </c>
       <c r="I7" t="n">
         <v>0.7387533875338753</v>
@@ -814,10 +814,10 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>0.7386870532775983</v>
+        <v>0.7386738015415047</v>
       </c>
       <c r="N7" t="n">
-        <v>1.731114576635897</v>
+        <v>1.731206586778251</v>
       </c>
     </row>
     <row r="8">
@@ -837,19 +837,19 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>10.3018645970276</v>
+        <v>10.33314369372474</v>
       </c>
       <c r="E8" t="n">
-        <v>746.4231518722319</v>
+        <v>754.1163739650934</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.5305324884502591</v>
+        <v>-0.5304439252401376</v>
       </c>
       <c r="G8" t="n">
-        <v>0.8119272427410865</v>
+        <v>0.8119375471117908</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.6534236819781638</v>
+        <v>-0.6533063129387512</v>
       </c>
       <c r="I8" t="n">
         <v>0.5751178664414889</v>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>0.6836676584138365</v>
+        <v>0.6837516130023644</v>
       </c>
       <c r="N8" t="n">
-        <v>1.102011295195952</v>
+        <v>1.102152079639353</v>
       </c>
     </row>
     <row r="9">
@@ -891,19 +891,19 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>7.257150331777682</v>
+        <v>7.240712634236365</v>
       </c>
       <c r="E9" t="n">
-        <v>164.9194414775531</v>
+        <v>165.8381586465032</v>
       </c>
       <c r="F9" t="n">
-        <v>0.4040201285942755</v>
+        <v>0.400884907979395</v>
       </c>
       <c r="G9" t="n">
-        <v>0.4826805244371472</v>
+        <v>0.4826876779894799</v>
       </c>
       <c r="H9" t="n">
-        <v>0.8370342455092892</v>
+        <v>0.8305265003846488</v>
       </c>
       <c r="I9" t="n">
         <v>0.2154834665412946</v>
@@ -922,10 +922,10 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>0.6830555734829968</v>
+        <v>0.6830148589620129</v>
       </c>
       <c r="N9" t="n">
-        <v>0.6545453048182865</v>
+        <v>0.6545109239730008</v>
       </c>
     </row>
     <row r="10">
@@ -945,19 +945,19 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>7.196336088817682</v>
+        <v>7.207543817403542</v>
       </c>
       <c r="E10" t="n">
-        <v>261.3952331292615</v>
+        <v>258.2943406863712</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.1980360012199773</v>
+        <v>-0.1954326849553631</v>
       </c>
       <c r="G10" t="n">
-        <v>0.9683185709702108</v>
+        <v>0.9683285279499275</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.2045153394316855</v>
+        <v>-0.201824772599769</v>
       </c>
       <c r="I10" t="n">
         <v>0.6126386245816655</v>
@@ -976,45 +976,45 @@
         </is>
       </c>
       <c r="M10" t="n">
-        <v>0.7132434911383944</v>
+        <v>0.7132503613065139</v>
       </c>
       <c r="N10" t="n">
-        <v>1.37113423565255</v>
+        <v>1.37115092949229</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>DOT</t>
+          <t>LTC</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>DOT</t>
+          <t>LTC</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Polkadot</t>
+          <t>Litecoin</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>6.947648675735286</v>
+        <v>6.927710582463343</v>
       </c>
       <c r="E11" t="n">
-        <v>223.5976023234206</v>
+        <v>461.2137800060078</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.2281757963002916</v>
+        <v>1.112448582455214</v>
       </c>
       <c r="G11" t="n">
-        <v>0.6646278686940342</v>
+        <v>0.8299407546221466</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.3433136151041145</v>
+        <v>1.34039517430577</v>
       </c>
       <c r="I11" t="n">
-        <v>0.4207389749702026</v>
+        <v>0.3268819295856837</v>
       </c>
       <c r="J11" t="n">
         <v>263</v>
@@ -1030,45 +1030,45 @@
         </is>
       </c>
       <c r="M11" t="n">
-        <v>0.7887005675498857</v>
+        <v>0.6626838420819338</v>
       </c>
       <c r="N11" t="n">
-        <v>1.04067374469445</v>
+        <v>1.091877729861527</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>LTC</t>
+          <t>DOT</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>LTC</t>
+          <t>DOT</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Litecoin</t>
+          <t>Polkadot</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>6.897476547321964</v>
+        <v>6.65295798881597</v>
       </c>
       <c r="E12" t="n">
-        <v>464.3456260135105</v>
+        <v>221.8111256255652</v>
       </c>
       <c r="F12" t="n">
-        <v>1.097849180532594</v>
+        <v>-0.2268104235504073</v>
       </c>
       <c r="G12" t="n">
-        <v>0.8298120817556376</v>
+        <v>0.6646995309748848</v>
       </c>
       <c r="H12" t="n">
-        <v>1.323009395343906</v>
+        <v>-0.3412224817095247</v>
       </c>
       <c r="I12" t="n">
-        <v>0.3268819295856837</v>
+        <v>0.4207389749702026</v>
       </c>
       <c r="J12" t="n">
         <v>263</v>
@@ -1084,10 +1084,10 @@
         </is>
       </c>
       <c r="M12" t="n">
-        <v>0.6627224123525529</v>
+        <v>0.788693866049147</v>
       </c>
       <c r="N12" t="n">
-        <v>1.091780437635067</v>
+        <v>1.040769054601677</v>
       </c>
     </row>
     <row r="13">
@@ -1107,19 +1107,19 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>4.82925591340638</v>
+        <v>4.844284108012606</v>
       </c>
       <c r="E13" t="n">
-        <v>101.0197736586972</v>
+        <v>100.9611074138145</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.363058996185505</v>
+        <v>-0.3592483490829504</v>
       </c>
       <c r="G13" t="n">
-        <v>0.8596025375910525</v>
+        <v>0.8596438463220787</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.4223568222622287</v>
+        <v>-0.4179037058427945</v>
       </c>
       <c r="I13" t="n">
         <v>0.4691011235955056</v>
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="M13" t="n">
-        <v>0.760385259670406</v>
+        <v>0.7603847864693807</v>
       </c>
       <c r="N13" t="n">
-        <v>1.297643138990007</v>
+        <v>1.29769464649612</v>
       </c>
     </row>
     <row r="14">
@@ -1161,19 +1161,19 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>4.813855107047473</v>
+        <v>4.812668819814019</v>
       </c>
       <c r="E14" t="n">
-        <v>194.0849738246058</v>
+        <v>192.9663791753172</v>
       </c>
       <c r="F14" t="n">
-        <v>1.895572967645</v>
+        <v>1.893948773691809</v>
       </c>
       <c r="G14" t="n">
-        <v>0.8681583852948888</v>
+        <v>0.8681519972473337</v>
       </c>
       <c r="H14" t="n">
-        <v>2.183441408564093</v>
+        <v>2.181586611212079</v>
       </c>
       <c r="I14" t="n">
         <v>0.3000688231245698</v>
@@ -1192,10 +1192,10 @@
         </is>
       </c>
       <c r="M14" t="n">
-        <v>0.6021518474963754</v>
+        <v>0.6021696316524228</v>
       </c>
       <c r="N14" t="n">
-        <v>1.037836365384522</v>
+        <v>1.037851347597893</v>
       </c>
     </row>
     <row r="15">
@@ -1215,19 +1215,19 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>4.37142206673539</v>
+        <v>4.383778357666912</v>
       </c>
       <c r="E15" t="n">
-        <v>681.6620630120982</v>
+        <v>636.5057496666844</v>
       </c>
       <c r="F15" t="n">
-        <v>0.04371472593327974</v>
+        <v>0.0514093559578348</v>
       </c>
       <c r="G15" t="n">
-        <v>0.7988500589039178</v>
+        <v>0.7985908892291462</v>
       </c>
       <c r="H15" t="n">
-        <v>0.0547220663578089</v>
+        <v>0.06437508447843499</v>
       </c>
       <c r="I15" t="n">
         <v>0.4268646717284502</v>
@@ -1246,10 +1246,10 @@
         </is>
       </c>
       <c r="M15" t="n">
-        <v>0.7167542938177917</v>
+        <v>0.7169516618977084</v>
       </c>
       <c r="N15" t="n">
-        <v>1.136735626645271</v>
+        <v>1.136670953752824</v>
       </c>
     </row>
     <row r="16">
@@ -1269,19 +1269,19 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>4.320072916529446</v>
+        <v>4.303562814774951</v>
       </c>
       <c r="E16" t="n">
-        <v>370.0369556812129</v>
+        <v>360.9334657353577</v>
       </c>
       <c r="F16" t="n">
-        <v>0.6290625364289599</v>
+        <v>0.6276335926283987</v>
       </c>
       <c r="G16" t="n">
-        <v>0.9656664002290563</v>
+        <v>0.9656954904281111</v>
       </c>
       <c r="H16" t="n">
-        <v>0.6514284190479717</v>
+        <v>0.6499290913641492</v>
       </c>
       <c r="I16" t="n">
         <v>0.3858131487889274</v>
@@ -1300,10 +1300,10 @@
         </is>
       </c>
       <c r="M16" t="n">
-        <v>0.5131038238708179</v>
+        <v>0.5130174851775204</v>
       </c>
       <c r="N16" t="n">
-        <v>0.9836854972393428</v>
+        <v>0.9835419905172174</v>
       </c>
     </row>
     <row r="17">
@@ -1323,19 +1323,19 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>3.597518089330997</v>
+        <v>3.597303603631044</v>
       </c>
       <c r="E17" t="n">
-        <v>145.0249844792187</v>
+        <v>143.2963882516334</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.1442547629139544</v>
+        <v>-0.1452091481353439</v>
       </c>
       <c r="G17" t="n">
-        <v>0.7585081619513988</v>
+        <v>0.7584577775545802</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.1901822157626269</v>
+        <v>-0.1914531730474533</v>
       </c>
       <c r="I17" t="n">
         <v>0.4720416124837452</v>
@@ -1354,10 +1354,10 @@
         </is>
       </c>
       <c r="M17" t="n">
-        <v>0.7229508629889076</v>
+        <v>0.7230676454289811</v>
       </c>
       <c r="N17" t="n">
-        <v>1.088661677791776</v>
+        <v>1.088756782072341</v>
       </c>
     </row>
     <row r="18">
@@ -1377,19 +1377,19 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>3.275535649535071</v>
+        <v>3.283383232933775</v>
       </c>
       <c r="E18" t="n">
-        <v>70.08529916224686</v>
+        <v>69.40550338898005</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.4399255442547443</v>
+        <v>-0.4376987716221601</v>
       </c>
       <c r="G18" t="n">
-        <v>0.7545779741262876</v>
+        <v>0.7546221588537716</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.5830087271817419</v>
+        <v>-0.5800237463037128</v>
       </c>
       <c r="I18" t="n">
         <v>0.4644343302990898</v>
@@ -1408,10 +1408,10 @@
         </is>
       </c>
       <c r="M18" t="n">
-        <v>0.7641923008506487</v>
+        <v>0.764184253316926</v>
       </c>
       <c r="N18" t="n">
-        <v>1.144802788706236</v>
+        <v>1.144848905950673</v>
       </c>
     </row>
     <row r="19">
@@ -1431,19 +1431,19 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>2.998233406709849</v>
+        <v>2.991187229407598</v>
       </c>
       <c r="E19" t="n">
-        <v>109.8086863677731</v>
+        <v>108.5593272322631</v>
       </c>
       <c r="F19" t="n">
-        <v>0.135073286169676</v>
+        <v>0.1273915323945569</v>
       </c>
       <c r="G19" t="n">
-        <v>0.4862681719613752</v>
+        <v>0.486466395882367</v>
       </c>
       <c r="H19" t="n">
-        <v>0.2777752975788121</v>
+        <v>0.261871186731183</v>
       </c>
       <c r="I19" t="n">
         <v>0.2812667740203972</v>
@@ -1462,10 +1462,10 @@
         </is>
       </c>
       <c r="M19" t="n">
-        <v>0.7184967821852415</v>
+        <v>0.7180861083477031</v>
       </c>
       <c r="N19" t="n">
-        <v>0.6936247294605331</v>
+        <v>0.6935054940116393</v>
       </c>
     </row>
     <row r="20">
@@ -1485,19 +1485,19 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>2.65922158515475</v>
+        <v>2.662429925978806</v>
       </c>
       <c r="E20" t="n">
-        <v>114.6212853911332</v>
+        <v>113.4481108624429</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.3038382463367422</v>
+        <v>-0.3007330297530054</v>
       </c>
       <c r="G20" t="n">
-        <v>0.7873042411171082</v>
+        <v>0.7873080331475314</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.3859222781597432</v>
+        <v>-0.3819763257726749</v>
       </c>
       <c r="I20" t="n">
         <v>0.443815987933635</v>
@@ -1516,10 +1516,10 @@
         </is>
       </c>
       <c r="M20" t="n">
-        <v>0.732014496190137</v>
+        <v>0.732030563862382</v>
       </c>
       <c r="N20" t="n">
-        <v>1.144158441464198</v>
+        <v>1.144180210826205</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/MOZAIC/data/universe_last2023-07-21.xlsx
+++ b/tame_output/MOZAIC/data/universe_last2023-07-21.xlsx
@@ -513,19 +513,19 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>581.8129676216543</v>
+        <v>581.7155819801078</v>
       </c>
       <c r="E2" t="n">
-        <v>10974.52677257587</v>
+        <v>10986.04806802703</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6916213117292849</v>
+        <v>0.6913593026599691</v>
       </c>
       <c r="G2" t="n">
-        <v>0.5037087147506278</v>
+        <v>0.503707978273971</v>
       </c>
       <c r="H2" t="n">
-        <v>1.373058062081946</v>
+        <v>1.372539908994519</v>
       </c>
       <c r="I2" t="n">
         <v>0.2590724514387045</v>
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>227.9470433499902</v>
+        <v>227.6341782131447</v>
       </c>
       <c r="E3" t="n">
-        <v>4684.236035670167</v>
+        <v>4665.833651986193</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2946271220043644</v>
+        <v>0.2922659824284179</v>
       </c>
       <c r="G3" t="n">
-        <v>0.6047187047164361</v>
+        <v>0.6047200249904189</v>
       </c>
       <c r="H3" t="n">
-        <v>0.4872135088702449</v>
+        <v>0.4833079282152903</v>
       </c>
       <c r="I3" t="n">
         <v>0.3295577524045769</v>
@@ -598,10 +598,10 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>0.8908981672270467</v>
+        <v>0.8908834442507176</v>
       </c>
       <c r="N3" t="n">
-        <v>1.069552243078627</v>
+        <v>1.06953846654742</v>
       </c>
     </row>
     <row r="4">
@@ -621,19 +621,19 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>40.70623346966742</v>
+        <v>40.61617290651454</v>
       </c>
       <c r="E4" t="n">
-        <v>1873.558364564341</v>
+        <v>1871.475418441197</v>
       </c>
       <c r="F4" t="n">
-        <v>1.033660409935516</v>
+        <v>1.031837395198078</v>
       </c>
       <c r="G4" t="n">
-        <v>1.119640648982156</v>
+        <v>1.119663130014697</v>
       </c>
       <c r="H4" t="n">
-        <v>0.9232072905491568</v>
+        <v>0.9215605725844823</v>
       </c>
       <c r="I4" t="n">
         <v>0.3422195892575038</v>
@@ -652,10 +652,10 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>0.4716011478790175</v>
+        <v>0.471596619218861</v>
       </c>
       <c r="N4" t="n">
-        <v>1.048272145804352</v>
+        <v>1.048284660068933</v>
       </c>
     </row>
     <row r="5">
@@ -675,19 +675,19 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>37.52182154641338</v>
+        <v>37.48681967268329</v>
       </c>
       <c r="E5" t="n">
-        <v>414.2290470393924</v>
+        <v>412.5289835519888</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.3309897492190856</v>
+        <v>-0.3313705533397638</v>
       </c>
       <c r="G5" t="n">
-        <v>0.5683197560479892</v>
+        <v>0.568315214446476</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.5824005688641531</v>
+        <v>-0.5830752809644731</v>
       </c>
       <c r="I5" t="n">
         <v>0.3496897913141569</v>
@@ -706,10 +706,10 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>0.7367658595825548</v>
+        <v>0.7367656089134923</v>
       </c>
       <c r="N5" t="n">
-        <v>0.831271290967718</v>
+        <v>0.8312655806271886</v>
       </c>
     </row>
     <row r="6">
@@ -729,19 +729,19 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>10.95388873837297</v>
+        <v>10.97575519877694</v>
       </c>
       <c r="E6" t="n">
-        <v>207.6948224905358</v>
+        <v>207.8668236760578</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.3018591648373</v>
+        <v>-0.2996913505350001</v>
       </c>
       <c r="G6" t="n">
-        <v>0.7217952433476782</v>
+        <v>0.7217597086682078</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.4182060876950098</v>
+        <v>-0.4152231649062137</v>
       </c>
       <c r="I6" t="n">
         <v>0.4277673545966229</v>
@@ -760,10 +760,10 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>0.7500348382924856</v>
+        <v>0.7500965932423564</v>
       </c>
       <c r="N6" t="n">
-        <v>1.074771118249521</v>
+        <v>1.074808265826499</v>
       </c>
     </row>
     <row r="7">
@@ -783,19 +783,19 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>10.42603281206487</v>
+        <v>10.39747234172834</v>
       </c>
       <c r="E7" t="n">
-        <v>408.0746393534303</v>
+        <v>409.8145950812831</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.2756095963649136</v>
+        <v>-0.2791128399448246</v>
       </c>
       <c r="G7" t="n">
-        <v>1.180526293167712</v>
+        <v>1.18046827961477</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.2334633272973268</v>
+        <v>-0.2364424735206856</v>
       </c>
       <c r="I7" t="n">
         <v>0.7387533875338753</v>
@@ -814,10 +814,10 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>0.7386738015415047</v>
+        <v>0.7386878040376956</v>
       </c>
       <c r="N7" t="n">
-        <v>1.731206586778251</v>
+        <v>1.731156858370236</v>
       </c>
     </row>
     <row r="8">
@@ -837,19 +837,19 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>10.33314369372474</v>
+        <v>10.31138225158729</v>
       </c>
       <c r="E8" t="n">
-        <v>754.1163739650934</v>
+        <v>758.7343909930453</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.5304439252401376</v>
+        <v>-0.531152300178876</v>
       </c>
       <c r="G8" t="n">
-        <v>0.8119375471117908</v>
+        <v>0.8118560550930067</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.6533063129387512</v>
+        <v>-0.6542444277489892</v>
       </c>
       <c r="I8" t="n">
         <v>0.5751178664414889</v>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>0.6837516130023644</v>
+        <v>0.683796069660657</v>
       </c>
       <c r="N8" t="n">
-        <v>1.102152079639353</v>
+        <v>1.102114724299356</v>
       </c>
     </row>
     <row r="9">
@@ -891,19 +891,19 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>7.240712634236365</v>
+        <v>7.232508815083498</v>
       </c>
       <c r="E9" t="n">
-        <v>165.8381586465032</v>
+        <v>165.3251506365857</v>
       </c>
       <c r="F9" t="n">
-        <v>0.400884907979395</v>
+        <v>0.398474533175581</v>
       </c>
       <c r="G9" t="n">
-        <v>0.4826876779894799</v>
+        <v>0.4826981844652328</v>
       </c>
       <c r="H9" t="n">
-        <v>0.8305265003846488</v>
+        <v>0.8255148786545351</v>
       </c>
       <c r="I9" t="n">
         <v>0.2154834665412946</v>
@@ -922,10 +922,10 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>0.6830148589620129</v>
+        <v>0.6829860159122613</v>
       </c>
       <c r="N9" t="n">
-        <v>0.6545109239730008</v>
+        <v>0.6544984874483714</v>
       </c>
     </row>
     <row r="10">
@@ -945,19 +945,19 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>7.207543817403542</v>
+        <v>7.189028239542773</v>
       </c>
       <c r="E10" t="n">
-        <v>258.2943406863712</v>
+        <v>255.8263245517695</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.1954326849553631</v>
+        <v>-0.1952879871600173</v>
       </c>
       <c r="G10" t="n">
-        <v>0.9683285279499275</v>
+        <v>0.9683293087924699</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.201824772599769</v>
+        <v>-0.2016751794939948</v>
       </c>
       <c r="I10" t="n">
         <v>0.6126386245816655</v>
@@ -976,10 +976,10 @@
         </is>
       </c>
       <c r="M10" t="n">
-        <v>0.7132503613065139</v>
+        <v>0.713250378213742</v>
       </c>
       <c r="N10" t="n">
-        <v>1.37115092949229</v>
+        <v>1.3711540724416</v>
       </c>
     </row>
     <row r="11">
@@ -999,19 +999,19 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>6.927710582463343</v>
+        <v>6.913875732811838</v>
       </c>
       <c r="E11" t="n">
-        <v>461.2137800060078</v>
+        <v>458.2579740467089</v>
       </c>
       <c r="F11" t="n">
-        <v>1.112448582455214</v>
+        <v>1.10530065915801</v>
       </c>
       <c r="G11" t="n">
-        <v>0.8299407546221466</v>
+        <v>0.8298724539672272</v>
       </c>
       <c r="H11" t="n">
-        <v>1.34039517430577</v>
+        <v>1.33189221292271</v>
       </c>
       <c r="I11" t="n">
         <v>0.3268819295856837</v>
@@ -1030,10 +1030,10 @@
         </is>
       </c>
       <c r="M11" t="n">
-        <v>0.6626838420819338</v>
+        <v>0.6627135321095301</v>
       </c>
       <c r="N11" t="n">
-        <v>1.091877729861527</v>
+        <v>1.091838384322538</v>
       </c>
     </row>
     <row r="12">
@@ -1053,19 +1053,19 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>6.65295798881597</v>
+        <v>6.642296442823225</v>
       </c>
       <c r="E12" t="n">
-        <v>221.8111256255652</v>
+        <v>220.2827412219927</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.2268104235504073</v>
+        <v>-0.2272005988612722</v>
       </c>
       <c r="G12" t="n">
-        <v>0.6646995309748848</v>
+        <v>0.6646786977502648</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.3412224817095247</v>
+        <v>-0.3418201901614676</v>
       </c>
       <c r="I12" t="n">
         <v>0.4207389749702026</v>
@@ -1084,10 +1084,10 @@
         </is>
       </c>
       <c r="M12" t="n">
-        <v>0.788693866049147</v>
+        <v>0.7887036352214415</v>
       </c>
       <c r="N12" t="n">
-        <v>1.040769054601677</v>
+        <v>1.04075084727912</v>
       </c>
     </row>
     <row r="13">
@@ -1107,19 +1107,19 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>4.844284108012606</v>
+        <v>4.841148758172331</v>
       </c>
       <c r="E13" t="n">
-        <v>100.9611074138145</v>
+        <v>103.0557342981007</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.3592483490829504</v>
+        <v>-0.3579767228607923</v>
       </c>
       <c r="G13" t="n">
-        <v>0.8596438463220787</v>
+        <v>0.8596642274241365</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.4179037058427945</v>
+        <v>-0.4164145854171685</v>
       </c>
       <c r="I13" t="n">
         <v>0.4691011235955056</v>
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="M13" t="n">
-        <v>0.7603847864693807</v>
+        <v>0.7603757374712028</v>
       </c>
       <c r="N13" t="n">
-        <v>1.29769464649612</v>
+        <v>1.29771186699311</v>
       </c>
     </row>
     <row r="14">
@@ -1161,19 +1161,19 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>4.812668819814019</v>
+        <v>4.795559750348739</v>
       </c>
       <c r="E14" t="n">
-        <v>192.9663791753172</v>
+        <v>193.3622228320414</v>
       </c>
       <c r="F14" t="n">
-        <v>1.893948773691809</v>
+        <v>1.879342497063448</v>
       </c>
       <c r="G14" t="n">
-        <v>0.8681519972473337</v>
+        <v>0.8681064208753693</v>
       </c>
       <c r="H14" t="n">
-        <v>2.181586611212079</v>
+        <v>2.164875701723738</v>
       </c>
       <c r="I14" t="n">
         <v>0.3000688231245698</v>
@@ -1192,10 +1192,10 @@
         </is>
       </c>
       <c r="M14" t="n">
-        <v>0.6021696316524228</v>
+        <v>0.6021714575359791</v>
       </c>
       <c r="N14" t="n">
-        <v>1.037851347597893</v>
+        <v>1.037801526483934</v>
       </c>
     </row>
     <row r="15">
@@ -1215,19 +1215,19 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>4.383778357666912</v>
+        <v>4.38600860594243</v>
       </c>
       <c r="E15" t="n">
-        <v>636.5057496666844</v>
+        <v>605.1779179915578</v>
       </c>
       <c r="F15" t="n">
-        <v>0.0514093559578348</v>
+        <v>0.05158848866345078</v>
       </c>
       <c r="G15" t="n">
-        <v>0.7985908892291462</v>
+        <v>0.798585400452505</v>
       </c>
       <c r="H15" t="n">
-        <v>0.06437508447843499</v>
+        <v>0.06459983945889698</v>
       </c>
       <c r="I15" t="n">
         <v>0.4268646717284502</v>
@@ -1246,10 +1246,10 @@
         </is>
       </c>
       <c r="M15" t="n">
-        <v>0.7169516618977084</v>
+        <v>0.7169688334204183</v>
       </c>
       <c r="N15" t="n">
-        <v>1.136670953752824</v>
+        <v>1.136692027215796</v>
       </c>
     </row>
     <row r="16">
@@ -1269,19 +1269,19 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>4.303562814774951</v>
+        <v>4.295029216267607</v>
       </c>
       <c r="E16" t="n">
-        <v>360.9334657353577</v>
+        <v>357.0391642695185</v>
       </c>
       <c r="F16" t="n">
-        <v>0.6276335926283987</v>
+        <v>0.6133634539701922</v>
       </c>
       <c r="G16" t="n">
-        <v>0.9656954904281111</v>
+        <v>0.9660156053986138</v>
       </c>
       <c r="H16" t="n">
-        <v>0.6499290913641492</v>
+        <v>0.6349415584410728</v>
       </c>
       <c r="I16" t="n">
         <v>0.3858131487889274</v>
@@ -1300,10 +1300,10 @@
         </is>
       </c>
       <c r="M16" t="n">
-        <v>0.5130174851775204</v>
+        <v>0.5128181759645375</v>
       </c>
       <c r="N16" t="n">
-        <v>0.9835419905172174</v>
+        <v>0.9834872229169829</v>
       </c>
     </row>
     <row r="17">
@@ -1323,19 +1323,19 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>3.597303603631044</v>
+        <v>3.591196452326138</v>
       </c>
       <c r="E17" t="n">
-        <v>143.2963882516334</v>
+        <v>139.1733794869097</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.1452091481353439</v>
+        <v>-0.1440638501601677</v>
       </c>
       <c r="G17" t="n">
-        <v>0.7584577775545802</v>
+        <v>0.7585183880632833</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.1914531730474533</v>
+        <v>-0.18992796012237</v>
       </c>
       <c r="I17" t="n">
         <v>0.4720416124837452</v>
@@ -1354,10 +1354,10 @@
         </is>
       </c>
       <c r="M17" t="n">
-        <v>0.7230676454289811</v>
+        <v>0.723006046396388</v>
       </c>
       <c r="N17" t="n">
-        <v>1.088756782072341</v>
+        <v>1.088752619626583</v>
       </c>
     </row>
     <row r="18">
@@ -1377,19 +1377,19 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>3.283383232933775</v>
+        <v>3.272111601958886</v>
       </c>
       <c r="E18" t="n">
-        <v>69.40550338898005</v>
+        <v>68.9381079808926</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.4376987716221601</v>
+        <v>-0.4390186386675272</v>
       </c>
       <c r="G18" t="n">
-        <v>0.7546221588537716</v>
+        <v>0.7545941582222817</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.5800237463037128</v>
+        <v>-0.581794377658308</v>
       </c>
       <c r="I18" t="n">
         <v>0.4644343302990898</v>
@@ -1408,10 +1408,10 @@
         </is>
       </c>
       <c r="M18" t="n">
-        <v>0.764184253316926</v>
+        <v>0.7641952113019098</v>
       </c>
       <c r="N18" t="n">
-        <v>1.144848905950673</v>
+        <v>1.144824515517629</v>
       </c>
     </row>
     <row r="19">
@@ -1431,19 +1431,19 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>2.991187229407598</v>
+        <v>2.966973048091438</v>
       </c>
       <c r="E19" t="n">
-        <v>108.5593272322631</v>
+        <v>109.1967719099375</v>
       </c>
       <c r="F19" t="n">
-        <v>0.1273915323945569</v>
+        <v>0.1178098754580996</v>
       </c>
       <c r="G19" t="n">
-        <v>0.486466395882367</v>
+        <v>0.4868061295210621</v>
       </c>
       <c r="H19" t="n">
-        <v>0.261871186731183</v>
+        <v>0.2420057355769233</v>
       </c>
       <c r="I19" t="n">
         <v>0.2812667740203972</v>
@@ -1462,10 +1462,10 @@
         </is>
       </c>
       <c r="M19" t="n">
-        <v>0.7180861083477031</v>
+        <v>0.7175171347371122</v>
       </c>
       <c r="N19" t="n">
-        <v>0.6935054940116393</v>
+        <v>0.6934409504953948</v>
       </c>
     </row>
     <row r="20">
@@ -1485,19 +1485,19 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>2.662429925978806</v>
+        <v>2.663865701536868</v>
       </c>
       <c r="E20" t="n">
-        <v>113.4481108624429</v>
+        <v>112.6172741650594</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.3007330297530054</v>
+        <v>-0.3002151183457269</v>
       </c>
       <c r="G20" t="n">
-        <v>0.7873080331475314</v>
+        <v>0.7873104052983677</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.3819763257726749</v>
+        <v>-0.3813173512319504</v>
       </c>
       <c r="I20" t="n">
         <v>0.443815987933635</v>
@@ -1516,10 +1516,10 @@
         </is>
       </c>
       <c r="M20" t="n">
-        <v>0.732030563862382</v>
+        <v>0.7320329046853713</v>
       </c>
       <c r="N20" t="n">
-        <v>1.144180210826205</v>
+        <v>1.144188989927228</v>
       </c>
     </row>
   </sheetData>
